--- a/part3_regression_insights/analysis/regression_workbook.xlsx
+++ b/part3_regression_insights/analysis/regression_workbook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mitali Kalburgi\OneDrive\Desktop\Bitsom Notes\Assignments\Final Capstone Project\part3_regression_insights\part3_regression_insights\analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED059F37-E0A6-4C53-AF0E-C30F58D64FB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2D61D7-B213-4C1A-ADEC-FA3DE3660713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11110" yWindow="0" windowWidth="11380" windowHeight="13370" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" firstSheet="4" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="original_datasheet" sheetId="1" r:id="rId1"/>
@@ -648,7 +648,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -683,11 +683,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -707,22 +722,174 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="8">
     <dxf>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF365F91"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="165" formatCode="mmm/yyyy"/>
@@ -2150,7 +2317,7 @@
     <tableColumn id="1" xr3:uid="{167553A2-EE6D-4247-BF81-0DE961976EB2}" name="store_id">
       <calculatedColumnFormula>dummy_variable_creation_sheet!A2</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{66F7583D-94A8-4CBF-AADE-EB5CA8AF9D1C}" name="month" dataDxfId="2">
+    <tableColumn id="2" xr3:uid="{66F7583D-94A8-4CBF-AADE-EB5CA8AF9D1C}" name="month" dataDxfId="7">
       <calculatedColumnFormula>dummy_variable_creation_sheet!B2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{AF803E17-EBB9-433C-99F4-1CCC4B78C5B4}" name="region">
@@ -2174,16 +2341,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9F35372-8813-4BB1-8AD9-CA1CDA447ECE}" name="Table3" displayName="Table3" ref="A3:F8" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{C9F35372-8813-4BB1-8AD9-CA1CDA447ECE}" name="Table3" displayName="Table3" ref="A3:F8" totalsRowShown="0" headerRowDxfId="6">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{D7A88C4D-5456-4DC7-A884-C5C052E5AF08}" name="Model Name" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{E58D5FC6-8CE9-4592-A322-819F88FB7322}" name="Variables Used"/>
-    <tableColumn id="3" xr3:uid="{F6F99025-35B2-4924-B30C-5CDEFE648885}" name="R-squared"/>
-    <tableColumn id="4" xr3:uid="{85CC1BAB-3CC3-4E3D-AE7A-758E63AE9461}" name="Significant Variables"/>
-    <tableColumn id="5" xr3:uid="{7F8632DE-C9EF-41B0-AA38-6340855D7C32}" name="Business Usefulness"/>
-    <tableColumn id="6" xr3:uid="{4104F8B2-C888-42C6-9567-C682E4117448}" name="Limitations"/>
+    <tableColumn id="1" xr3:uid="{D7A88C4D-5456-4DC7-A884-C5C052E5AF08}" name="Model Name" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E58D5FC6-8CE9-4592-A322-819F88FB7322}" name="Variables Used" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{F6F99025-35B2-4924-B30C-5CDEFE648885}" name="R-squared" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{85CC1BAB-3CC3-4E3D-AE7A-758E63AE9461}" name="Significant Variables" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{7F8632DE-C9EF-41B0-AA38-6340855D7C32}" name="Business Usefulness" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{4104F8B2-C888-42C6-9567-C682E4117448}" name="Limitations" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -80072,22 +80239,22 @@
       <c r="A2" s="8"/>
     </row>
     <row r="3" spans="1:6" ht="28">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="1" t="s">
         <v>164</v>
       </c>
     </row>
@@ -80098,7 +80265,7 @@
       <c r="B4" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="12">
         <v>0.16700000000000001</v>
       </c>
       <c r="D4" s="11" t="s">
@@ -80107,21 +80274,21 @@
       <c r="E4" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="13" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="56">
-      <c r="A5" t="s">
+      <c r="A5" s="12" t="s">
         <v>156</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="12">
         <v>0.73599999999999999</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="12" t="s">
         <v>176</v>
       </c>
       <c r="E5" s="11" t="s">
@@ -80138,10 +80305,10 @@
       <c r="B6" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="12">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="12" t="s">
         <v>177</v>
       </c>
       <c r="E6" s="11" t="s">
@@ -80158,7 +80325,7 @@
       <c r="B7" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="12">
         <v>1.2999999999999999E-2</v>
       </c>
       <c r="D7" s="11" t="s">
@@ -80178,7 +80345,7 @@
       <c r="B8" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="12">
         <v>0.82099999999999995</v>
       </c>
       <c r="D8" s="11" t="s">
